--- a/public/plantilla-control-presupuestal.xlsx
+++ b/public/plantilla-control-presupuestal.xlsx
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +97,17 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -287,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -307,13 +318,13 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -322,31 +333,31 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -394,17 +405,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -417,7 +428,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -432,13 +443,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -468,10 +479,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,8 +500,54 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1005,10 +1062,10 @@
       </c>
       <c r="B10" s="76" t="n"/>
       <c r="C10" s="77" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="76" t="n"/>
-      <c r="F10" s="76" t="n"/>
-      <c r="G10" s="77" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="83" t="n"/>
+      <c r="F10" s="83" t="n"/>
+      <c r="G10" s="84" t="n"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t>Tipo de proyecto</t>
@@ -1016,10 +1073,10 @@
       </c>
       <c r="I10" s="76" t="n"/>
       <c r="J10" s="77" t="n"/>
-      <c r="K10" s="23" t="n"/>
-      <c r="L10" s="76" t="n"/>
-      <c r="M10" s="76" t="n"/>
-      <c r="N10" s="77" t="n"/>
+      <c r="K10" s="82" t="n"/>
+      <c r="L10" s="83" t="n"/>
+      <c r="M10" s="83" t="n"/>
+      <c r="N10" s="84" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="33">
       <c r="A11" s="21" t="inlineStr">
@@ -1029,10 +1086,10 @@
       </c>
       <c r="B11" s="76" t="n"/>
       <c r="C11" s="77" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="76" t="n"/>
-      <c r="F11" s="76" t="n"/>
-      <c r="G11" s="77" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="83" t="n"/>
+      <c r="F11" s="83" t="n"/>
+      <c r="G11" s="84" t="n"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t>Contratante</t>
@@ -1040,10 +1097,10 @@
       </c>
       <c r="I11" s="76" t="n"/>
       <c r="J11" s="77" t="n"/>
-      <c r="K11" s="23" t="n"/>
-      <c r="L11" s="76" t="n"/>
-      <c r="M11" s="76" t="n"/>
-      <c r="N11" s="77" t="n"/>
+      <c r="K11" s="82" t="n"/>
+      <c r="L11" s="83" t="n"/>
+      <c r="M11" s="83" t="n"/>
+      <c r="N11" s="84" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="33">
       <c r="A12" s="21" t="inlineStr">
@@ -1053,10 +1110,10 @@
       </c>
       <c r="B12" s="76" t="n"/>
       <c r="C12" s="77" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="76" t="n"/>
-      <c r="F12" s="76" t="n"/>
-      <c r="G12" s="77" t="n"/>
+      <c r="D12" s="82" t="n"/>
+      <c r="E12" s="83" t="n"/>
+      <c r="F12" s="83" t="n"/>
+      <c r="G12" s="84" t="n"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t>Fecha de corte</t>
@@ -1064,10 +1121,10 @@
       </c>
       <c r="I12" s="76" t="n"/>
       <c r="J12" s="77" t="n"/>
-      <c r="K12" s="23" t="n"/>
-      <c r="L12" s="76" t="n"/>
-      <c r="M12" s="76" t="n"/>
-      <c r="N12" s="77" t="n"/>
+      <c r="K12" s="82" t="n"/>
+      <c r="L12" s="83" t="n"/>
+      <c r="M12" s="83" t="n"/>
+      <c r="N12" s="84" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="33">
       <c r="A13" s="39" t="inlineStr">
@@ -1162,39 +1219,39 @@
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" s="33">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="8">
+      <c r="B15" s="82" t="n"/>
+      <c r="C15" s="86" t="n"/>
+      <c r="D15" s="86" t="n"/>
+      <c r="E15" s="87">
         <f>IF(AND(C15="",D15=""),"",N(C15)+N(D15))</f>
         <v/>
       </c>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="16">
+      <c r="F15" s="86" t="n"/>
+      <c r="G15" s="88">
         <f>IF(OR(E15="",E15=0),"",F15/E15)</f>
         <v/>
       </c>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8">
+      <c r="H15" s="87" t="n"/>
+      <c r="I15" s="87">
         <f>IF(OR(F15="",H15=""),"",H15-F15)</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="88">
         <f>IF(OR(I15="",F15=0),"",I15/F15)</f>
         <v/>
       </c>
-      <c r="K15" s="53">
+      <c r="K15" s="89">
         <f>IF(E15="","",E15-N(F15))</f>
         <v/>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="87">
         <f>IF(OR(F15="",F15=0,H15=""),"",H15/F15*E15)</f>
         <v/>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="88">
         <f>IF(OR(L15="",E15="",E15=0),"",L15/E15-1)</f>
         <v/>
       </c>
@@ -1204,39 +1261,39 @@
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" s="33">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="8">
+      <c r="B16" s="82" t="n"/>
+      <c r="C16" s="86" t="n"/>
+      <c r="D16" s="86" t="n"/>
+      <c r="E16" s="87">
         <f>IF(AND(C16="",D16=""),"",N(C16)+N(D16))</f>
         <v/>
       </c>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="16">
+      <c r="F16" s="86" t="n"/>
+      <c r="G16" s="88">
         <f>IF(OR(E16="",E16=0),"",F16/E16)</f>
         <v/>
       </c>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8">
+      <c r="H16" s="87" t="n"/>
+      <c r="I16" s="87">
         <f>IF(OR(F16="",H16=""),"",H16-F16)</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="88">
         <f>IF(OR(I16="",F16=0),"",I16/F16)</f>
         <v/>
       </c>
-      <c r="K16" s="53">
+      <c r="K16" s="89">
         <f>IF(E16="","",E16-N(F16))</f>
         <v/>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="87">
         <f>IF(OR(F16="",F16=0,H16=""),"",H16/F16*E16)</f>
         <v/>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="88">
         <f>IF(OR(L16="",E16="",E16=0),"",L16/E16-1)</f>
         <v/>
       </c>
@@ -1246,39 +1303,39 @@
       </c>
     </row>
     <row r="17" ht="22.05" customHeight="1" s="33">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="85" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="23" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="8">
+      <c r="B17" s="82" t="n"/>
+      <c r="C17" s="86" t="n"/>
+      <c r="D17" s="86" t="n"/>
+      <c r="E17" s="87">
         <f>IF(AND(C17="",D17=""),"",N(C17)+N(D17))</f>
         <v/>
       </c>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="16">
+      <c r="F17" s="86" t="n"/>
+      <c r="G17" s="88">
         <f>IF(OR(E17="",E17=0),"",F17/E17)</f>
         <v/>
       </c>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8">
+      <c r="H17" s="87" t="n"/>
+      <c r="I17" s="87">
         <f>IF(OR(F17="",H17=""),"",H17-F17)</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="88">
         <f>IF(OR(I17="",F17=0),"",I17/F17)</f>
         <v/>
       </c>
-      <c r="K17" s="53">
+      <c r="K17" s="89">
         <f>IF(E17="","",E17-N(F17))</f>
         <v/>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="87">
         <f>IF(OR(F17="",F17=0,H17=""),"",H17/F17*E17)</f>
         <v/>
       </c>
-      <c r="M17" s="16">
+      <c r="M17" s="88">
         <f>IF(OR(L17="",E17="",E17=0),"",L17/E17-1)</f>
         <v/>
       </c>
@@ -1288,39 +1345,39 @@
       </c>
     </row>
     <row r="18" ht="22.05" customHeight="1" s="33">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="85" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="23" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="8">
+      <c r="B18" s="82" t="n"/>
+      <c r="C18" s="86" t="n"/>
+      <c r="D18" s="86" t="n"/>
+      <c r="E18" s="87">
         <f>IF(AND(C18="",D18=""),"",N(C18)+N(D18))</f>
         <v/>
       </c>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="16">
+      <c r="F18" s="86" t="n"/>
+      <c r="G18" s="88">
         <f>IF(OR(E18="",E18=0),"",F18/E18)</f>
         <v/>
       </c>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8">
+      <c r="H18" s="87" t="n"/>
+      <c r="I18" s="87">
         <f>IF(OR(F18="",H18=""),"",H18-F18)</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="88">
         <f>IF(OR(I18="",F18=0),"",I18/F18)</f>
         <v/>
       </c>
-      <c r="K18" s="53">
+      <c r="K18" s="89">
         <f>IF(E18="","",E18-N(F18))</f>
         <v/>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="87">
         <f>IF(OR(F18="",F18=0,H18=""),"",H18/F18*E18)</f>
         <v/>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="88">
         <f>IF(OR(L18="",E18="",E18=0),"",L18/E18-1)</f>
         <v/>
       </c>
@@ -1330,39 +1387,39 @@
       </c>
     </row>
     <row r="19" ht="22.05" customHeight="1" s="33">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="85" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="23" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="8">
+      <c r="B19" s="82" t="n"/>
+      <c r="C19" s="86" t="n"/>
+      <c r="D19" s="86" t="n"/>
+      <c r="E19" s="87">
         <f>IF(AND(C19="",D19=""),"",N(C19)+N(D19))</f>
         <v/>
       </c>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="16">
+      <c r="F19" s="86" t="n"/>
+      <c r="G19" s="88">
         <f>IF(OR(E19="",E19=0),"",F19/E19)</f>
         <v/>
       </c>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8">
+      <c r="H19" s="87" t="n"/>
+      <c r="I19" s="87">
         <f>IF(OR(F19="",H19=""),"",H19-F19)</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="88">
         <f>IF(OR(I19="",F19=0),"",I19/F19)</f>
         <v/>
       </c>
-      <c r="K19" s="53">
+      <c r="K19" s="89">
         <f>IF(E19="","",E19-N(F19))</f>
         <v/>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="87">
         <f>IF(OR(F19="",F19=0,H19=""),"",H19/F19*E19)</f>
         <v/>
       </c>
-      <c r="M19" s="16">
+      <c r="M19" s="88">
         <f>IF(OR(L19="",E19="",E19=0),"",L19/E19-1)</f>
         <v/>
       </c>
@@ -1372,39 +1429,39 @@
       </c>
     </row>
     <row r="20" ht="22.05" customHeight="1" s="33">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="85" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="8">
+      <c r="B20" s="82" t="n"/>
+      <c r="C20" s="86" t="n"/>
+      <c r="D20" s="86" t="n"/>
+      <c r="E20" s="87">
         <f>IF(AND(C20="",D20=""),"",N(C20)+N(D20))</f>
         <v/>
       </c>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="16">
+      <c r="F20" s="86" t="n"/>
+      <c r="G20" s="88">
         <f>IF(OR(E20="",E20=0),"",F20/E20)</f>
         <v/>
       </c>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8">
+      <c r="H20" s="87" t="n"/>
+      <c r="I20" s="87">
         <f>IF(OR(F20="",H20=""),"",H20-F20)</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="88">
         <f>IF(OR(I20="",F20=0),"",I20/F20)</f>
         <v/>
       </c>
-      <c r="K20" s="53">
+      <c r="K20" s="89">
         <f>IF(E20="","",E20-N(F20))</f>
         <v/>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="87">
         <f>IF(OR(F20="",F20=0,H20=""),"",H20/F20*E20)</f>
         <v/>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="88">
         <f>IF(OR(L20="",E20="",E20=0),"",L20/E20-1)</f>
         <v/>
       </c>
@@ -1414,39 +1471,39 @@
       </c>
     </row>
     <row r="21" ht="22.05" customHeight="1" s="33">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="85" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="23" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="8">
+      <c r="B21" s="82" t="n"/>
+      <c r="C21" s="86" t="n"/>
+      <c r="D21" s="86" t="n"/>
+      <c r="E21" s="87">
         <f>IF(AND(C21="",D21=""),"",N(C21)+N(D21))</f>
         <v/>
       </c>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="16">
+      <c r="F21" s="86" t="n"/>
+      <c r="G21" s="88">
         <f>IF(OR(E21="",E21=0),"",F21/E21)</f>
         <v/>
       </c>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8">
+      <c r="H21" s="87" t="n"/>
+      <c r="I21" s="87">
         <f>IF(OR(F21="",H21=""),"",H21-F21)</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="88">
         <f>IF(OR(I21="",F21=0),"",I21/F21)</f>
         <v/>
       </c>
-      <c r="K21" s="53">
+      <c r="K21" s="89">
         <f>IF(E21="","",E21-N(F21))</f>
         <v/>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="87">
         <f>IF(OR(F21="",F21=0,H21=""),"",H21/F21*E21)</f>
         <v/>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="88">
         <f>IF(OR(L21="",E21="",E21=0),"",L21/E21-1)</f>
         <v/>
       </c>
@@ -1456,39 +1513,39 @@
       </c>
     </row>
     <row r="22" ht="22.05" customHeight="1" s="33">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="85" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="23" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="8">
+      <c r="B22" s="82" t="n"/>
+      <c r="C22" s="86" t="n"/>
+      <c r="D22" s="86" t="n"/>
+      <c r="E22" s="87">
         <f>IF(AND(C22="",D22=""),"",N(C22)+N(D22))</f>
         <v/>
       </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="16">
+      <c r="F22" s="86" t="n"/>
+      <c r="G22" s="88">
         <f>IF(OR(E22="",E22=0),"",F22/E22)</f>
         <v/>
       </c>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8">
+      <c r="H22" s="87" t="n"/>
+      <c r="I22" s="87">
         <f>IF(OR(F22="",H22=""),"",H22-F22)</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="88">
         <f>IF(OR(I22="",F22=0),"",I22/F22)</f>
         <v/>
       </c>
-      <c r="K22" s="53">
+      <c r="K22" s="89">
         <f>IF(E22="","",E22-N(F22))</f>
         <v/>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="87">
         <f>IF(OR(F22="",F22=0,H22=""),"",H22/F22*E22)</f>
         <v/>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="88">
         <f>IF(OR(L22="",E22="",E22=0),"",L22/E22-1)</f>
         <v/>
       </c>
@@ -1498,39 +1555,39 @@
       </c>
     </row>
     <row r="23" ht="22.05" customHeight="1" s="33">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="85" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="23" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="8">
+      <c r="B23" s="82" t="n"/>
+      <c r="C23" s="86" t="n"/>
+      <c r="D23" s="86" t="n"/>
+      <c r="E23" s="87">
         <f>IF(AND(C23="",D23=""),"",N(C23)+N(D23))</f>
         <v/>
       </c>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="16">
+      <c r="F23" s="86" t="n"/>
+      <c r="G23" s="88">
         <f>IF(OR(E23="",E23=0),"",F23/E23)</f>
         <v/>
       </c>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8">
+      <c r="H23" s="87" t="n"/>
+      <c r="I23" s="87">
         <f>IF(OR(F23="",H23=""),"",H23-F23)</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="88">
         <f>IF(OR(I23="",F23=0),"",I23/F23)</f>
         <v/>
       </c>
-      <c r="K23" s="53">
+      <c r="K23" s="89">
         <f>IF(E23="","",E23-N(F23))</f>
         <v/>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="87">
         <f>IF(OR(F23="",F23=0,H23=""),"",H23/F23*E23)</f>
         <v/>
       </c>
-      <c r="M23" s="16">
+      <c r="M23" s="88">
         <f>IF(OR(L23="",E23="",E23=0),"",L23/E23-1)</f>
         <v/>
       </c>
@@ -1540,39 +1597,39 @@
       </c>
     </row>
     <row r="24" ht="22.05" customHeight="1" s="33">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="85" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="23" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="8">
+      <c r="B24" s="82" t="n"/>
+      <c r="C24" s="86" t="n"/>
+      <c r="D24" s="86" t="n"/>
+      <c r="E24" s="87">
         <f>IF(AND(C24="",D24=""),"",N(C24)+N(D24))</f>
         <v/>
       </c>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="16">
+      <c r="F24" s="86" t="n"/>
+      <c r="G24" s="88">
         <f>IF(OR(E24="",E24=0),"",F24/E24)</f>
         <v/>
       </c>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8">
+      <c r="H24" s="87" t="n"/>
+      <c r="I24" s="87">
         <f>IF(OR(F24="",H24=""),"",H24-F24)</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="88">
         <f>IF(OR(I24="",F24=0),"",I24/F24)</f>
         <v/>
       </c>
-      <c r="K24" s="53">
+      <c r="K24" s="89">
         <f>IF(E24="","",E24-N(F24))</f>
         <v/>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="87">
         <f>IF(OR(F24="",F24=0,H24=""),"",H24/F24*E24)</f>
         <v/>
       </c>
-      <c r="M24" s="16">
+      <c r="M24" s="88">
         <f>IF(OR(L24="",E24="",E24=0),"",L24/E24-1)</f>
         <v/>
       </c>
@@ -1582,39 +1639,39 @@
       </c>
     </row>
     <row r="25" ht="22.05" customHeight="1" s="33">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="85" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="23" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="8">
+      <c r="B25" s="82" t="n"/>
+      <c r="C25" s="86" t="n"/>
+      <c r="D25" s="86" t="n"/>
+      <c r="E25" s="87">
         <f>IF(AND(C25="",D25=""),"",N(C25)+N(D25))</f>
         <v/>
       </c>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="16">
+      <c r="F25" s="86" t="n"/>
+      <c r="G25" s="88">
         <f>IF(OR(E25="",E25=0),"",F25/E25)</f>
         <v/>
       </c>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8">
+      <c r="H25" s="87" t="n"/>
+      <c r="I25" s="87">
         <f>IF(OR(F25="",H25=""),"",H25-F25)</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="88">
         <f>IF(OR(I25="",F25=0),"",I25/F25)</f>
         <v/>
       </c>
-      <c r="K25" s="53">
+      <c r="K25" s="89">
         <f>IF(E25="","",E25-N(F25))</f>
         <v/>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="87">
         <f>IF(OR(F25="",F25=0,H25=""),"",H25/F25*E25)</f>
         <v/>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="88">
         <f>IF(OR(L25="",E25="",E25=0),"",L25/E25-1)</f>
         <v/>
       </c>
@@ -1624,39 +1681,39 @@
       </c>
     </row>
     <row r="26" ht="22.05" customHeight="1" s="33">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="85" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="23" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="8">
+      <c r="B26" s="82" t="n"/>
+      <c r="C26" s="86" t="n"/>
+      <c r="D26" s="86" t="n"/>
+      <c r="E26" s="87">
         <f>IF(AND(C26="",D26=""),"",N(C26)+N(D26))</f>
         <v/>
       </c>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="16">
+      <c r="F26" s="86" t="n"/>
+      <c r="G26" s="88">
         <f>IF(OR(E26="",E26=0),"",F26/E26)</f>
         <v/>
       </c>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8">
+      <c r="H26" s="87" t="n"/>
+      <c r="I26" s="87">
         <f>IF(OR(F26="",H26=""),"",H26-F26)</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="88">
         <f>IF(OR(I26="",F26=0),"",I26/F26)</f>
         <v/>
       </c>
-      <c r="K26" s="53">
+      <c r="K26" s="89">
         <f>IF(E26="","",E26-N(F26))</f>
         <v/>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="87">
         <f>IF(OR(F26="",F26=0,H26=""),"",H26/F26*E26)</f>
         <v/>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="88">
         <f>IF(OR(L26="",E26="",E26=0),"",L26/E26-1)</f>
         <v/>
       </c>
@@ -1666,39 +1723,39 @@
       </c>
     </row>
     <row r="27" ht="22.05" customHeight="1" s="33">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="85" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="23" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="8">
+      <c r="B27" s="82" t="n"/>
+      <c r="C27" s="86" t="n"/>
+      <c r="D27" s="86" t="n"/>
+      <c r="E27" s="87">
         <f>IF(AND(C27="",D27=""),"",N(C27)+N(D27))</f>
         <v/>
       </c>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="16">
+      <c r="F27" s="86" t="n"/>
+      <c r="G27" s="88">
         <f>IF(OR(E27="",E27=0),"",F27/E27)</f>
         <v/>
       </c>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8">
+      <c r="H27" s="87" t="n"/>
+      <c r="I27" s="87">
         <f>IF(OR(F27="",H27=""),"",H27-F27)</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="88">
         <f>IF(OR(I27="",F27=0),"",I27/F27)</f>
         <v/>
       </c>
-      <c r="K27" s="53">
+      <c r="K27" s="89">
         <f>IF(E27="","",E27-N(F27))</f>
         <v/>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="87">
         <f>IF(OR(F27="",F27=0,H27=""),"",H27/F27*E27)</f>
         <v/>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="88">
         <f>IF(OR(L27="",E27="",E27=0),"",L27/E27-1)</f>
         <v/>
       </c>
@@ -1708,39 +1765,39 @@
       </c>
     </row>
     <row r="28" ht="22.05" customHeight="1" s="33">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="85" t="n">
         <v>14</v>
       </c>
-      <c r="B28" s="23" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="8">
+      <c r="B28" s="82" t="n"/>
+      <c r="C28" s="86" t="n"/>
+      <c r="D28" s="86" t="n"/>
+      <c r="E28" s="87">
         <f>IF(AND(C28="",D28=""),"",N(C28)+N(D28))</f>
         <v/>
       </c>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="16">
+      <c r="F28" s="86" t="n"/>
+      <c r="G28" s="88">
         <f>IF(OR(E28="",E28=0),"",F28/E28)</f>
         <v/>
       </c>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8">
+      <c r="H28" s="87" t="n"/>
+      <c r="I28" s="87">
         <f>IF(OR(F28="",H28=""),"",H28-F28)</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="88">
         <f>IF(OR(I28="",F28=0),"",I28/F28)</f>
         <v/>
       </c>
-      <c r="K28" s="53">
+      <c r="K28" s="89">
         <f>IF(E28="","",E28-N(F28))</f>
         <v/>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="87">
         <f>IF(OR(F28="",F28=0,H28=""),"",H28/F28*E28)</f>
         <v/>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="88">
         <f>IF(OR(L28="",E28="",E28=0),"",L28/E28-1)</f>
         <v/>
       </c>
@@ -1750,39 +1807,39 @@
       </c>
     </row>
     <row r="29" ht="22.05" customHeight="1" s="33">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="85" t="n">
         <v>15</v>
       </c>
-      <c r="B29" s="23" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="8">
+      <c r="B29" s="82" t="n"/>
+      <c r="C29" s="86" t="n"/>
+      <c r="D29" s="86" t="n"/>
+      <c r="E29" s="87">
         <f>IF(AND(C29="",D29=""),"",N(C29)+N(D29))</f>
         <v/>
       </c>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="16">
+      <c r="F29" s="86" t="n"/>
+      <c r="G29" s="88">
         <f>IF(OR(E29="",E29=0),"",F29/E29)</f>
         <v/>
       </c>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8">
+      <c r="H29" s="87" t="n"/>
+      <c r="I29" s="87">
         <f>IF(OR(F29="",H29=""),"",H29-F29)</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="88">
         <f>IF(OR(I29="",F29=0),"",I29/F29)</f>
         <v/>
       </c>
-      <c r="K29" s="53">
+      <c r="K29" s="89">
         <f>IF(E29="","",E29-N(F29))</f>
         <v/>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="87">
         <f>IF(OR(F29="",F29=0,H29=""),"",H29/F29*E29)</f>
         <v/>
       </c>
-      <c r="M29" s="16">
+      <c r="M29" s="88">
         <f>IF(OR(L29="",E29="",E29=0),"",L29/E29-1)</f>
         <v/>
       </c>
@@ -1792,39 +1849,39 @@
       </c>
     </row>
     <row r="30" ht="22.05" customHeight="1" s="33">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="85" t="n">
         <v>16</v>
       </c>
-      <c r="B30" s="23" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="8">
+      <c r="B30" s="82" t="n"/>
+      <c r="C30" s="86" t="n"/>
+      <c r="D30" s="86" t="n"/>
+      <c r="E30" s="87">
         <f>IF(AND(C30="",D30=""),"",N(C30)+N(D30))</f>
         <v/>
       </c>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="16">
+      <c r="F30" s="86" t="n"/>
+      <c r="G30" s="88">
         <f>IF(OR(E30="",E30=0),"",F30/E30)</f>
         <v/>
       </c>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8">
+      <c r="H30" s="87" t="n"/>
+      <c r="I30" s="87">
         <f>IF(OR(F30="",H30=""),"",H30-F30)</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="88">
         <f>IF(OR(I30="",F30=0),"",I30/F30)</f>
         <v/>
       </c>
-      <c r="K30" s="53">
+      <c r="K30" s="89">
         <f>IF(E30="","",E30-N(F30))</f>
         <v/>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="87">
         <f>IF(OR(F30="",F30=0,H30=""),"",H30/F30*E30)</f>
         <v/>
       </c>
-      <c r="M30" s="16">
+      <c r="M30" s="88">
         <f>IF(OR(L30="",E30="",E30=0),"",L30/E30-1)</f>
         <v/>
       </c>
@@ -1840,47 +1897,47 @@
         </is>
       </c>
       <c r="B31" s="77" t="n"/>
-      <c r="C31" s="9">
+      <c r="C31" s="90">
         <f>SUM(C15:C30)</f>
         <v/>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="90">
         <f>SUM(D15:D30)</f>
         <v/>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="90">
         <f>SUM(E15:E30)</f>
         <v/>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="90">
         <f>SUM(F15:F30)</f>
         <v/>
       </c>
-      <c r="G31" s="18">
+      <c r="G31" s="91">
         <f>IF(E31=0,"",F31/E31)</f>
         <v/>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="90">
         <f>SUM(H15:H30)</f>
         <v/>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="90">
         <f>SUM(I15:I30)</f>
         <v/>
       </c>
-      <c r="J31" s="18">
+      <c r="J31" s="91">
         <f>IF(F31=0,"",I31/F31)</f>
         <v/>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="90">
         <f>SUM(K15:K30)</f>
         <v/>
       </c>
-      <c r="L31" s="9">
+      <c r="L31" s="90">
         <f>SUM(L15:L30)</f>
         <v/>
       </c>
-      <c r="M31" s="18">
+      <c r="M31" s="91">
         <f>IF(OR(L31=0,E31=0),"",L31/E31-1)</f>
         <v/>
       </c>
@@ -1919,7 +1976,7 @@
       <c r="B34" s="76" t="n"/>
       <c r="C34" s="76" t="n"/>
       <c r="D34" s="77" t="n"/>
-      <c r="E34" s="43">
+      <c r="E34" s="92">
         <f>E31</f>
         <v/>
       </c>
@@ -1949,8 +2006,8 @@
       <c r="B35" s="76" t="n"/>
       <c r="C35" s="76" t="n"/>
       <c r="D35" s="77" t="n"/>
-      <c r="E35" s="44" t="n"/>
-      <c r="F35" s="77" t="n"/>
+      <c r="E35" s="93" t="n"/>
+      <c r="F35" s="84" t="n"/>
       <c r="H35" s="48" t="n"/>
       <c r="N35" s="49" t="n"/>
     </row>
@@ -1963,7 +2020,7 @@
       <c r="B36" s="76" t="n"/>
       <c r="C36" s="76" t="n"/>
       <c r="D36" s="77" t="n"/>
-      <c r="E36" s="43">
+      <c r="E36" s="92">
         <f>E34*(1+E35)</f>
         <v/>
       </c>
@@ -1980,7 +2037,7 @@
       <c r="B37" s="76" t="n"/>
       <c r="C37" s="76" t="n"/>
       <c r="D37" s="77" t="n"/>
-      <c r="E37" s="43">
+      <c r="E37" s="92">
         <f>F31</f>
         <v/>
       </c>
@@ -1997,7 +2054,7 @@
       <c r="B38" s="76" t="n"/>
       <c r="C38" s="76" t="n"/>
       <c r="D38" s="77" t="n"/>
-      <c r="E38" s="43">
+      <c r="E38" s="92">
         <f>H31</f>
         <v/>
       </c>
@@ -2014,7 +2071,7 @@
       <c r="B39" s="76" t="n"/>
       <c r="C39" s="76" t="n"/>
       <c r="D39" s="77" t="n"/>
-      <c r="E39" s="43">
+      <c r="E39" s="92">
         <f>F31-H31</f>
         <v/>
       </c>
@@ -2031,7 +2088,7 @@
       <c r="B40" s="76" t="n"/>
       <c r="C40" s="76" t="n"/>
       <c r="D40" s="77" t="n"/>
-      <c r="E40" s="44">
+      <c r="E40" s="94">
         <f>G31</f>
         <v/>
       </c>
@@ -2097,10 +2154,10 @@
       </c>
       <c r="B44" s="76" t="n"/>
       <c r="C44" s="77" t="n"/>
-      <c r="D44" s="23" t="n"/>
-      <c r="E44" s="76" t="n"/>
-      <c r="F44" s="76" t="n"/>
-      <c r="G44" s="77" t="n"/>
+      <c r="D44" s="82" t="n"/>
+      <c r="E44" s="83" t="n"/>
+      <c r="F44" s="83" t="n"/>
+      <c r="G44" s="84" t="n"/>
       <c r="H44" s="21" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -2108,10 +2165,10 @@
       </c>
       <c r="I44" s="76" t="n"/>
       <c r="J44" s="77" t="n"/>
-      <c r="K44" s="23" t="n"/>
-      <c r="L44" s="76" t="n"/>
-      <c r="M44" s="76" t="n"/>
-      <c r="N44" s="77" t="n"/>
+      <c r="K44" s="95" t="n"/>
+      <c r="L44" s="83" t="n"/>
+      <c r="M44" s="83" t="n"/>
+      <c r="N44" s="84" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="33">
       <c r="A45" s="21" t="inlineStr">
@@ -2121,10 +2178,10 @@
       </c>
       <c r="B45" s="76" t="n"/>
       <c r="C45" s="77" t="n"/>
-      <c r="D45" s="23" t="n"/>
-      <c r="E45" s="76" t="n"/>
-      <c r="F45" s="76" t="n"/>
-      <c r="G45" s="77" t="n"/>
+      <c r="D45" s="82" t="n"/>
+      <c r="E45" s="83" t="n"/>
+      <c r="F45" s="83" t="n"/>
+      <c r="G45" s="84" t="n"/>
       <c r="H45" s="21" t="inlineStr">
         <is>
           <t>Nombre:</t>
@@ -2132,10 +2189,10 @@
       </c>
       <c r="I45" s="76" t="n"/>
       <c r="J45" s="77" t="n"/>
-      <c r="K45" s="23" t="n"/>
-      <c r="L45" s="76" t="n"/>
-      <c r="M45" s="76" t="n"/>
-      <c r="N45" s="77" t="n"/>
+      <c r="K45" s="95" t="n"/>
+      <c r="L45" s="83" t="n"/>
+      <c r="M45" s="83" t="n"/>
+      <c r="N45" s="84" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="33">
       <c r="A46" s="21" t="inlineStr">
@@ -2145,10 +2202,10 @@
       </c>
       <c r="B46" s="76" t="n"/>
       <c r="C46" s="77" t="n"/>
-      <c r="D46" s="23" t="n"/>
-      <c r="E46" s="76" t="n"/>
-      <c r="F46" s="76" t="n"/>
-      <c r="G46" s="77" t="n"/>
+      <c r="D46" s="82" t="n"/>
+      <c r="E46" s="83" t="n"/>
+      <c r="F46" s="83" t="n"/>
+      <c r="G46" s="84" t="n"/>
       <c r="H46" s="21" t="inlineStr">
         <is>
           <t>Cargo:</t>
@@ -2156,12 +2213,13 @@
       </c>
       <c r="I46" s="76" t="n"/>
       <c r="J46" s="77" t="n"/>
-      <c r="K46" s="23" t="n"/>
-      <c r="L46" s="76" t="n"/>
-      <c r="M46" s="76" t="n"/>
-      <c r="N46" s="77" t="n"/>
+      <c r="K46" s="95" t="n"/>
+      <c r="L46" s="83" t="n"/>
+      <c r="M46" s="83" t="n"/>
+      <c r="N46" s="84" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="60">
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="H46:J46"/>
